--- a/bom/BOM_CitriBot.xlsx
+++ b/bom/BOM_CitriBot.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>J3 prismático (NEMA 14), en zócalo de la RAMPS</t>
+          <t>J3 prismático (NEMA 17 + husillo T8), en zócalo de la RAMPS</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>El laboratorio tiene 14: conviene pedir 1 de repuesto</t>
+          <t>El laboratorio tiene 14: conviene pedir 1 de repuesto. Con un NEMA 17 de 1,7 A, regular a ≈ 1,2 A y poner disipador</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12 V, 12 rpm, eje D8</t>
+          <t>12 V, 12 rpm (9 con carga), eje D8 con plano a 7, fijación 4 × M4 prof. 6</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -1027,7 +1027,7 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Confirmar si los 90 kg·cm son torque nominal o de bloqueo. Medir agujeros con calibre antes de imprimir CB-210</t>
+          <t>Un vendedor da ≈ 70 kg·cm sin decir si es nominal o de bloqueo (bloqueo 6,5 A). El hombro pide 25 kg·cm de pico (control/torques.py). Medir con calibre antes de imprimir CB-210</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Motor paso a paso NEMA 14</t>
+          <t>Motor paso a paso NEMA 17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35 mm, eje Ø5 (tipo SM35HT36)</t>
+          <t>40 mm, ≈ 4,5 kg·cm, 1,7 A, eje Ø5 (tipo 17HS4401)</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>J3 prismático (dentro de E2)</t>
+          <t>J3 prismático (atrás de E2, mueve el husillo T8)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Un NEMA 17 no entra en E2 sin rediseñar la parte trasera</t>
+          <t>El 17HS2408 del riel (M04) es más corto y tiene menos torque: no sirve para J3. CAD: CB-505</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Tuerca/rosca para varilla</t>
+          <t>Husillo T8 + tuerca de brida</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Según pedido</t>
+          <t>Ø8, avance 8 mm (4 entradas × paso 2), largo 400 mm</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Prismático (diseño anterior con husillo)</t>
+          <t>J3 prismático (carrera 350 mm)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Pedido 'Rosca p/ Varilla'. Con el tornillo TSF-E3 impreso puede no usarse</t>
+          <t>Pedido 'Rosca p/ Varilla': confirmar largo (≥ 400 mm) y avance. CAD: CB-511 y CB-512</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Prisionero</t>
+          <t>Acople flexible</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>M3 × 4</t>
+          <t>5 × 8 mm, Ø19 × 25</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tornillo TSF-E3 al eje del NEMA 14</t>
+          <t>NEMA 17 → husillo T8 de J3</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Alternativa: epoxi</t>
+          <t>CAD: CB-513</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>4 NEMA 14 → E2 · 4 AS5600 → tapa de E2</t>
+          <t>4 NEMA 17 → placa de E2 · 4 AS5600 → tapa de E2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>3 tapa de E2 → E2 · 4 Sabertooth → bandeja · 8 pestañas de los servos · 2 porta-servo</t>
+          <t>3 tapa de E2 → E2 · 4 Sabertooth → bandeja · 8 pestañas de los servos · 2 porta-servo · 4 tuerca T8 → portatuerca</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M5 × 40</t>
+          <t>Tornillo M5 × 25</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Horquilla → E3</t>
+          <t>Horquilla → brida de E3</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3311,7 +3311,7 @@
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>No modelado: verificar largo</t>
+          <t>No modelado: brida de 10 mm + placa de la horquilla de 8 mm + tuerca</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M6 × 10 Allen</t>
+          <t>Tornillo M4 × 10 Allen</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Motor 5840 → torre</t>
+          <t>Motor 5840 → torre (rosca M4 prof. 6 del motor)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>8 rodillos · 4 patas · 4 horquilla → E3</t>
+          <t>8 rodillos · 4 patas · 4 horquilla → brida de E3</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>H21</t>
+          <t>H22</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3786,16 +3786,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Arandela M5 ancha</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>DIN 9021</t>
-        </is>
-      </c>
+          <t>Separador M5 × 10</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3804,7 +3800,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Horquilla → E3 (agujeros de E3 de Ø10.2)</t>
+          <t>Rodillos de la lazy susan</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3825,7 +3821,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>H22</t>
+          <t>H23</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3835,12 +3831,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Separador M5 × 10</t>
+          <t>Separador M8 × 20</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3849,7 +3845,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Rodillos de la lazy susan</t>
+          <t>Eje central de J1</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3870,7 +3866,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>H23</t>
+          <t>H24</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3880,7 +3876,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Separador M8 × 20</t>
+          <t>Tornillo M3 × 35 + tuerca</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -3894,7 +3890,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Eje central de J1</t>
+          <t>Pasantes: tubo de E3 → brida y portatuerca</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3910,7 +3906,11 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>No modelado; además pegar con epoxi</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Buje D8 en E2</t>
+          <t>Buje D8 en E2 · tapones del tubo de E3</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4111,36 +4111,40 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>X05</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>CB-112 Pata de la base</t>
+          <t>Tubo cuadrado de aluminio</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>30 × 30 × 2 mm, largo 460 mm</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Eslabón E3 (prismático J3)</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4149,18 +4153,18 @@
         </is>
       </c>
       <c r="J72" s="3" t="n"/>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>CAD: CB-401. Se desliza en el canal 31 × 31 de E2: cinta de PTFE si hay juego</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4170,7 +4174,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CB-121 Placa fija J1 (1M2A)</t>
+          <t>CB-112 Pata de la base</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4179,7 +4183,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4209,7 +4213,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4219,7 +4223,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CB-131 Soporte motor J1 (37D)</t>
+          <t>CB-121 Placa fija J1 (1M2A)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4258,7 +4262,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4268,7 +4272,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CB-141 Bandeja de electrónica</t>
+          <t>CB-131 Soporte motor J1 (37D)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4302,16 +4306,12 @@
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>210 × 100 mm</t>
-        </is>
-      </c>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CB-201 Plato giratorio con dientes T5 (1M1B)</t>
+          <t>CB-141 Bandeja de electrónica</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4355,12 +4355,16 @@
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>210 × 100 mm</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4370,7 +4374,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CB-210 Torre de cintura (2M1D mod)</t>
+          <t>CB-201 Plato giratorio con dientes T5 (1M1B)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4404,16 +4408,12 @@
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>318 mm de alto: hay que partirla para la Ender 3 V2</t>
-        </is>
-      </c>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CB-232 Soporte del imán</t>
+          <t>CB-210 Torre de cintura (2M1D mod)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4457,12 +4457,16 @@
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>318 mm de alto: hay que partirla para la Ender 3 V2</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4472,7 +4476,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CB-301 Eslabón E2</t>
+          <t>CB-232 Soporte del imán</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4506,16 +4510,12 @@
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>260 mm: hay que partirlo</t>
-        </is>
-      </c>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>CB-302 Tornillo sinfín TSF-E3</t>
+          <t>CB-301 Eslabón E2</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>PETG: cubo ≥ 6 perímetros 50 %, cola 3 perímetros 15 %</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
@@ -4561,14 +4561,14 @@
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 % o mecanizado</t>
+          <t>504,5 mm de largo: partir en 3 tramos (cubo del hombro + 2 tramos de cola). La cola liviana es parte del balance de J2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>CB-303 Tapa de E2 / soporte AS5600</t>
+          <t>CB-402 Brida de E3 (herramienta)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4612,12 +4612,16 @@
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Tapón al 100 % de relleno</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4627,7 +4631,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>CB-305 Buje D8 del hombro</t>
+          <t>CB-303 Tapa de E2 / soporte AS5600</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4661,16 +4665,12 @@
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>PETG al 100 % o aluminio</t>
-        </is>
-      </c>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>CB-401 Eslabón E3</t>
+          <t>CB-305 Buje D8 del hombro</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4714,12 +4714,16 @@
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Mejor en aluminio: transmite el torque del hombro (≈ 25 kg·cm de pico)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>CB-601 Horquilla U</t>
+          <t>CB-403 Portatuerca T8</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4763,12 +4767,16 @@
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4778,7 +4786,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>CB-602 Porta-servo</t>
+          <t>CB-601 Horquilla U</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4817,7 +4825,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4827,7 +4835,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CB-603 Caja de torsión</t>
+          <t>CB-602 Porta-servo</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4866,7 +4874,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4876,7 +4884,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CB-604 Tapa de la caja</t>
+          <t>CB-603 Caja de torsión</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4915,7 +4923,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4925,7 +4933,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CB-605 Polea del servo GT2 66 dientes</t>
+          <t>CB-604 Tapa de la caja</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4959,16 +4967,12 @@
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %</t>
-        </is>
-      </c>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4978,7 +4982,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CB-606 Eje hueco con polea GT2 66 dientes</t>
+          <t>CB-605 Polea del servo GT2 66 dientes</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5021,7 +5025,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5031,7 +5035,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>CB-607 Separador del pivote</t>
+          <t>CB-606 Eje hueco con polea GT2 66 dientes</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5065,12 +5069,16 @@
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5080,7 +5088,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Anillo de retención del eje hueco</t>
+          <t>CB-607 Separador del pivote</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5114,14 +5122,63 @@
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Anillo de retención del eje hueco</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>Solo en el .scad (pieza 5), no en el STEP de la herramienta</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
+  <autoFilter ref="A1:M92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/bom/BOM_CitriBot.xlsx
+++ b/bom/BOM_CitriBot.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>J3 prismático (NEMA 17 + husillo T8), en zócalo de la RAMPS</t>
+          <t>J3 prismático (NEMA 17 + correa GT2), en zócalo de la RAMPS</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Un vendedor da ≈ 70 kg·cm sin decir si es nominal o de bloqueo (bloqueo 6,5 A). El hombro pide 25 kg·cm de pico (control/torques.py). Medir con calibre antes de imprimir CB-210</t>
+          <t>Un vendedor da ≈ 70 kg·cm sin decir si es nominal o de bloqueo (bloqueo 6,5 A). Con la v7 el hombro pide ≈ 39 kg·cm de pico (control/torques.py): probar colgando 1 kg a 40 cm del eje. Medir con calibre antes de imprimir CB-210</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>J3 prismático (atrás de E2, mueve el husillo T8)</t>
+          <t>J3 prismático (sobre el cubo de E2, mueve la correa GT2)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>El 17HS2408 del riel (M04) es más corto y tiene menos torque: no sirve para J3. CAD: CB-505</t>
+          <t>El 17HS2408 del riel (M04) es más corto y tiene menos torque: no sirve para J3. CAD: CB-505 sobre la placa CB-306</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cámara web USB</t>
+          <t>Cámara web USB Logitech C270</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>720p, 30 fps</t>
+          <t>720p, 30 fps, foco fijo, ~55° de campo diagonal</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Visión estéreo</t>
+          <t>Visión estéreo, en el mástil CB-150 (a 120 mm entre lentes)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Precio del pedido 'Cámaras': confirmar si es por unidad o por las dos</t>
+          <t>Precio del pedido 'Cámaras': confirmar si es por unidad o por las dos. CAD: CB-515. Quitarles la pinza de monitor</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Anotar el contenido real del kit</t>
+          <t>Anotar el contenido real del kit: puede cubrir la correa y las poleas de J3 (T07, T08, T09)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>J3 prismático (carrera 350 mm)</t>
+          <t>No se usa desde la v7 (J3 con correa GT2): queda de repuesto</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2186,14 +2186,14 @@
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Pedido 'Rosca p/ Varilla': confirmar largo (≥ 400 mm) y avance. CAD: CB-511 y CB-512</t>
+          <t>Ya pedido ('Rosca p/ Varilla'). Era el husillo de la v6 (CB-511 y CB-512, retirados del CAD)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Acople flexible</t>
+          <t>Polea GT2</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5 × 8 mm, Ø19 × 25</t>
+          <t>20 dientes, agujero 5 mm, correa de 6 mm, 2 prisioneros</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>NEMA 17 → husillo T8 de J3</t>
+          <t>Eje del NEMA 17 de J3</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2239,33 +2239,33 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>CAD: CB-513</t>
+          <t>CAD: HW_Polea_GT2_20T_D5. Puede venir en el kit T04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Rodamientos y bujes</t>
+          <t>Transmisión</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Rodamiento 625ZZ</t>
+          <t>Polea loca GT2 dentada</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>5 × 16 × 5 mm</t>
+          <t>20 dientes, agujero 5 mm, con rodamientos</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Rodillos de la lazy susan J1</t>
+          <t>Punta de la cola de E2 (J3)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2290,31 +2290,35 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>CAD: HW_Polea_Loca_GT2_20T_D5. Puede venir en el kit T04</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rodamientos y bujes</t>
+          <t>Transmisión</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Rodamiento 608ZZ</t>
+          <t>Correa GT2 abierta</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8 × 22 × 7 mm</t>
+          <t>6 mm de ancho, 1 m</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2 eje central de J1, 1 pivote de la muñeca</t>
+          <t>J3 prismático (lazo de 810 mm, extremos en la pinza CB-403)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2339,12 +2343,16 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>CAD: CB-514. Puede salir del kit T04</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2354,16 +2362,16 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Rodamiento 6806-ZZ</t>
+          <t>Rodamiento 625ZZ</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>30 × 42 × 7 mm</t>
+          <t>5 × 16 × 5 mm</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2372,38 +2380,28 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Eje hueco de la torsión</t>
+          <t>Rodillos de la lazy susan J1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Compra grupal</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Pedido</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>AliExpress</t>
-        </is>
-      </c>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Pedido 'Rodamientos': confirmar que son estos</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2413,16 +2411,16 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Buje autolubricado (bronce sinterizado)</t>
+          <t>Rodamiento 608ZZ</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>5 × 8 × 10 mm</t>
+          <t>8 × 22 × 7 mm</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2431,7 +2429,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Rodillos de la lazy susan</t>
+          <t>2 eje central de J1, 1 pivote de la muñeca</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2452,7 +2450,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2462,12 +2460,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Buje autolubricado (bronce sinterizado)</t>
+          <t>Rodamiento 6806-ZZ</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8 × 12 × 20 mm</t>
+          <t>30 × 42 × 7 mm</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
@@ -2480,47 +2478,57 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Eje central de J1</t>
+          <t>Eje hueco de la torsión</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Por comprar</t>
+          <t>Compra grupal</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Falta</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t>Pedido</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>AliExpress</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Pedido 'Rodamientos': confirmar que son estos</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>L01</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Riel J0</t>
+          <t>Rodamientos y bujes</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Estructura del riel</t>
+          <t>Buje autolubricado (bronce sinterizado)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1,2 m (perfil de aluminio o 2 varillas lisas)</t>
+          <t>5 × 8 × 10 mm</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2529,12 +2537,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Desplazamiento lineal de la base</t>
+          <t>Rodillos de la lazy susan</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Por definir</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2545,35 +2553,31 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Riel todavía sin diseñar</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>L02</t>
+          <t>R05</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Riel J0</t>
+          <t>Rodamientos y bujes</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Carro del riel</t>
+          <t>Buje autolubricado (bronce sinterizado)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Patines o rodamientos lineales</t>
+          <t>8 × 12 × 20 mm</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2582,12 +2586,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Lleva la base del brazo</t>
+          <t>Eje central de J1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Por definir</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2603,7 +2607,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>L03</t>
+          <t>L01</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2613,12 +2617,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Correa GT2 abierta + poleas</t>
+          <t>Estructura del riel</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>≈ 2,6 m, polea 20 dientes + polea tensora</t>
+          <t>1,2 m (perfil de aluminio o 2 varillas lisas)</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
@@ -2631,7 +2635,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Transmisión del riel</t>
+          <t>Desplazamiento lineal de la base</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2649,29 +2653,29 @@
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Revisar si el kit T04 la cubre</t>
+          <t>Riel todavía sin diseñar</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>L02</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Alimentación y cableado</t>
+          <t>Riel J0</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Fuente 12 V DC</t>
+          <t>Carro del riel</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Corriente a dimensionar (≥ 10 A estimado)</t>
+          <t>Patines o rodamientos lineales</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Motores DC, paso a paso y bomba</t>
+          <t>Lleva la base del brazo</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2700,31 +2704,27 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Sumar corriente de bloqueo de 37D + 5840 + paso a paso + bomba</t>
-        </is>
-      </c>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>L03</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Alimentación y cableado</t>
+          <t>Riel J0</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Regulador UBEC 6 V</t>
+          <t>Correa GT2 abierta + poleas</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>≥ 5 A</t>
+          <t>≈ 2,6 m, polea 20 dientes + polea tensora</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Servos MG996R</t>
+          <t>Transmisión del riel</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Por comprar</t>
+          <t>Por definir</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2755,14 +2755,14 @@
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>No alimentar los servos desde el 5 V del MEGA</t>
+          <t>Revisar si el kit T04 la cubre</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Parada de emergencia + fusible</t>
+          <t>Fuente 12 V DC</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Pulsador hongo NC, portafusible</t>
+          <t>Corriente a dimensionar (≥ 10 A estimado)</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Seguridad: corta la potencia de motores</t>
+          <t>Motores DC, paso a paso y bomba</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Por comprar</t>
+          <t>Por definir</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2806,12 +2806,16 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Sumar corriente de bloqueo de 37D + 5840 + paso a paso + bomba</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2821,12 +2825,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Cables, borneras y conectores</t>
+          <t>Regulador UBEC 6 V</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Dupont, JST, termocontraíble</t>
+          <t>≥ 5 A</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
@@ -2834,12 +2838,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>lote</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Cableado general</t>
+          <t>Servos MG996R</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2855,31 +2859,35 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>No alimentar los servos desde el 5 V del MEGA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>H01</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Tornillería</t>
+          <t>Alimentación y cableado</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M3 × 6 Allen</t>
+          <t>Parada de emergencia + fusible</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>DIN 912</t>
+          <t>Pulsador hongo NC, portafusible</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2888,7 +2896,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>4 NEMA 17 → placa de E2 · 4 AS5600 → tapa de E2</t>
+          <t>Seguridad: corta la potencia de motores</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2909,31 +2917,35 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>H02</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Tornillería</t>
+          <t>Alimentación y cableado</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M3 × 8</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>Cables, borneras y conectores</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Dupont, JST, termocontraíble</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>lote</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>6 motor 37D → soporte · 5 Arduino MEGA → bandeja · 2 anillo del eje hueco · 8 horns metálicos</t>
+          <t>Cableado general</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2954,7 +2966,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>H03</t>
+          <t>H01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2964,12 +2976,16 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M3 × 10</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>Tornillo M3 × 6 Allen</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2978,7 +2994,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>3 tapa de E2 → E2 · 4 Sabertooth → bandeja · 8 pestañas de los servos · 2 porta-servo · 4 tuerca T8 → portatuerca</t>
+          <t>4 NEMA 17 → placa CB-306 · 4 AS5600 → tapa de E2</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2999,7 +3015,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>H04</t>
+          <t>H02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3009,12 +3025,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M3 × 12</t>
+          <t>Tornillo M3 × 8</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3023,7 +3039,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Tapa de la caja de torsión</t>
+          <t>6 motor 37D → soporte · 5 Arduino MEGA → bandeja · 2 anillo del eje hueco · 8 horns metálicos</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3044,7 +3060,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>H05</t>
+          <t>H03</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3054,12 +3070,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M4 × 30</t>
+          <t>Tornillo M3 × 10</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3068,7 +3084,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>4 soporte motor J1 → tablero · 2 soporte del imán → torre · 4 bandeja → tablero</t>
+          <t>3 tapa de E2 → E2 · 4 Sabertooth → bandeja · 8 pestañas de los servos · 2 porta-servo · 4 placa CB-306 → insertos de E2 · 4 soportes C270 → barra estéreo</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3089,7 +3105,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>H06</t>
+          <t>H04</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3099,7 +3115,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M4 × 40</t>
+          <t>Tornillo M3 × 12</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -3113,7 +3129,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Placa fija 1M2A → tablero</t>
+          <t>Tapa de la caja de torsión</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3134,7 +3150,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H05</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3144,12 +3160,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M4 × 45</t>
+          <t>Tornillo M4 × 30</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3158,7 +3174,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Torre 2M1D → plato 1M1B</t>
+          <t>4 soporte motor J1 → tablero · 2 soporte del imán → torre · 4 bandeja → tablero</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3179,7 +3195,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>H08</t>
+          <t>H06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3189,12 +3205,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M5 × 20</t>
+          <t>Tornillo M4 × 40</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3203,7 +3219,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Ejes de los rodillos</t>
+          <t>Placa fija 1M2A → tablero</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3224,7 +3240,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>H09</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3234,12 +3250,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M5 × 30</t>
+          <t>Tornillo M4 × 45</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3248,7 +3264,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Patas → tablero</t>
+          <t>Torre 2M1D → plato 1M1B</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3269,7 +3285,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>H10</t>
+          <t>H08</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3279,12 +3295,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M5 × 25</t>
+          <t>Tornillo M5 × 20</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3293,7 +3309,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Horquilla → brida de E3</t>
+          <t>Ejes de los rodillos</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3309,16 +3325,12 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>No modelado: brida de 10 mm + placa de la horquilla de 8 mm + tuerca</t>
-        </is>
-      </c>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>H11</t>
+          <t>H09</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3328,16 +3340,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M4 × 10 Allen</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>DIN 912</t>
-        </is>
-      </c>
+          <t>Tornillo M5 × 30</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3346,7 +3354,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Motor 5840 → torre (rosca M4 prof. 6 del motor)</t>
+          <t>4 patas → tablero · 1 pivote de la barra estéreo (CB-153/154)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3367,7 +3375,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H10</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3377,12 +3385,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M8 × 25</t>
+          <t>Tornillo M5 × 25</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3391,7 +3399,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Pivote libre de la muñeca</t>
+          <t>Horquilla → brida de E3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3409,14 +3417,14 @@
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>No modelado</t>
+          <t>No modelado: brida de 10 mm + placa de la horquilla de 8 mm + tuerca</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>H13</t>
+          <t>H11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3426,12 +3434,16 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M8 × 65 hexagonal</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
+          <t>Tornillo M4 × 10 Allen</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>DIN 912</t>
+        </is>
+      </c>
       <c r="E57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3440,7 +3452,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Eje central de J1</t>
+          <t>Motor 5840 → torre (rosca M4 prof. 6 del motor)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3461,7 +3473,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>H14</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3471,12 +3483,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tuerca M4 autoblocante</t>
+          <t>Tornillo M8 × 25</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3485,7 +3497,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>6 torre/plato · 4 placa 1M2A · 4 soporte J1 · 4 bandeja</t>
+          <t>Pivote libre de la muñeca</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3501,12 +3513,16 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>No modelado</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>H15</t>
+          <t>H13</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3516,12 +3532,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Tuerca M4</t>
+          <t>Tornillo M8 × 65 hexagonal</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3530,7 +3546,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Soporte del imán (dentro de la torre)</t>
+          <t>Eje central de J1</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3551,7 +3567,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H14</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3561,12 +3577,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Tuerca M5 autoblocante</t>
+          <t>Tuerca M4 autoblocante</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3575,7 +3591,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>8 rodillos · 4 patas · 4 horquilla → brida de E3</t>
+          <t>6 torre/plato · 4 placa 1M2A · 4 soporte J1 · 4 bandeja</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3596,7 +3612,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>H17</t>
+          <t>H15</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3606,12 +3622,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Tuerca M8 autoblocante</t>
+          <t>Tuerca M4</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3620,7 +3636,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Eje central de J1</t>
+          <t>Soporte del imán (dentro de la torre)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3641,7 +3657,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>H18</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3651,12 +3667,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Tuerca M8</t>
+          <t>Tuerca M5 autoblocante</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3681,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Pivote libre de la muñeca</t>
+          <t>8 rodillos · 4 patas · 4 horquilla → brida de E3 · 1 eje de la polea loca de J3 · 1 pivote de la barra estéreo</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3686,7 +3702,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>H19</t>
+          <t>H17</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3696,12 +3712,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Arandela M4</t>
+          <t>Tuerca M8 autoblocante</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3710,7 +3726,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Bajo el tablero</t>
+          <t>Eje central de J1</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3731,7 +3747,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>H20</t>
+          <t>H18</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3741,12 +3757,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Arandela M5</t>
+          <t>Tuerca M8</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3755,7 +3771,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Patas</t>
+          <t>Pivote libre de la muñeca</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3776,7 +3792,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>H22</t>
+          <t>H19</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3786,12 +3802,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Separador M5 × 10</t>
+          <t>Arandela M4</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3800,7 +3816,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Rodillos de la lazy susan</t>
+          <t>Bajo el tablero</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3821,7 +3837,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>H23</t>
+          <t>H20</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3831,12 +3847,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Separador M8 × 20</t>
+          <t>Arandela M5</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3845,7 +3861,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Eje central de J1</t>
+          <t>4 patas · 2 polea loca de J3</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3866,7 +3882,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>H24</t>
+          <t>H22</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3876,12 +3892,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Tornillo M3 × 35 + tuerca</t>
+          <t>Separador M5 × 10</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3890,7 +3906,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Pasantes: tubo de E3 → brida y portatuerca</t>
+          <t>Rodillos de la lazy susan</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3906,35 +3922,27 @@
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>No modelado; además pegar con epoxi</t>
-        </is>
-      </c>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>X01</t>
+          <t>H23</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Tablero contrachapado o MDF</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>550 × 550 × 16 mm</t>
-        </is>
-      </c>
+          <t>Separador M8 × 20</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -3943,7 +3951,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Base del brazo</t>
+          <t>Eje central de J1</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3959,44 +3967,40 @@
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>Agujeros: Ø42 motor J1 y 4 × Ø4.5 bandeja (ver CB-111)</t>
-        </is>
-      </c>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>X02</t>
+          <t>H24</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Filamento PETG</t>
+          <t>Pasador de acero Ø3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>1,75 mm</t>
+          <t>Ø3 × 30 mm</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Tubo de E3 → brida CB-402 y tapón CB-403</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4014,24 +4018,24 @@
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Estimado 3–4 kg: calcular con el slicer</t>
+          <t>Al ras: el tubo desliza en el canal con 0,5 mm de juego (una cabeza de tornillo roza). Además pegar con epoxi</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>X03</t>
+          <t>H25</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Epoxi bicomponente</t>
+          <t>Tornillo M5 × 70</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -4045,7 +4049,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Buje D8 en E2 · tapones del tubo de E3</t>
+          <t>Eje vertical de la polea loca de J3 (atraviesa E2)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4066,22 +4070,26 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>X04</t>
+          <t>H26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Cianoacrilato</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
+          <t>Inserto térmico M3</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Para PETG, Ø ext. ≈ 4,6 mm, largo 5–6 mm</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4090,7 +4098,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Imán en el soporte CB-232</t>
+          <t>Placa CB-306 del NEMA 17 → E2</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4106,31 +4114,31 @@
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Colocar con soldador a ≈ 220 °C</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>X05</t>
+          <t>H27</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Tubo cuadrado de aluminio</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>30 × 30 × 2 mm, largo 460 mm</t>
-        </is>
-      </c>
+          <t>Tuerca M3</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4139,7 +4147,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Eslabón E3 (prismático J3)</t>
+          <t>Soportes C270 → barra estéreo</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4155,45 +4163,45 @@
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>CAD: CB-401. Se desliza en el canal 31 × 31 de E2: cinta de PTFE si hay juego</t>
-        </is>
-      </c>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>H28</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CB-112 Pata de la base</t>
+          <t>Prisionero M4 × 6</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>Allen, punta plana</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Pie y cabezal del mástil → tubo 20 × 20</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4202,47 +4210,51 @@
         </is>
       </c>
       <c r="J73" s="3" t="n"/>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Roscar el plástico o usar inserto M4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>H29</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>CB-121 Placa fija J1 (1M2A)</t>
+          <t>Tirafondo 4 × 12</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>Cabeza fresada</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Pie del mástil CB-151 → tablero</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4251,33 +4263,33 @@
         </is>
       </c>
       <c r="J74" s="3" t="n"/>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>No pasantes: debajo está la pata de la base</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>X01</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CB-131 Soporte motor J1 (37D)</t>
+          <t>Tablero contrachapado o MDF</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>550 × 550 × 16 mm</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
@@ -4288,10 +4300,14 @@
           <t>u</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Base del brazo</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4300,47 +4316,51 @@
         </is>
       </c>
       <c r="J75" s="3" t="n"/>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Agujeros: Ø42 motor J1 y 4 × Ø4.5 bandeja (ver CB-111)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>X02</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
+          <t>Materia prima y consumibles</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Filamento PETG</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>1,75 mm</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
           <t>Piezas impresas</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>CB-141 Bandeja de electrónica</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>PETG, ≥ 4 perímetros</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4349,39 +4369,31 @@
         </is>
       </c>
       <c r="J76" s="3" t="n"/>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>210 × 100 mm</t>
+          <t>Estimado 3–4 kg: calcular con el slicer</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>X03</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>CB-201 Plato giratorio con dientes T5 (1M1B)</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>PETG, ≥ 4 perímetros</t>
-        </is>
-      </c>
+          <t>Epoxi bicomponente</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
@@ -4390,10 +4402,14 @@
           <t>u</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Buje D8 en E2 · brida y tapón del tubo de E3</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4402,35 +4418,27 @@
         </is>
       </c>
       <c r="J77" s="3" t="n"/>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>X04</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CB-210 Torre de cintura (2M1D mod)</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>PETG, ≥ 4 perímetros</t>
-        </is>
-      </c>
+          <t>Cianoacrilato</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="n">
         <v>1</v>
       </c>
@@ -4439,10 +4447,14 @@
           <t>u</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Imán en el soporte CB-232</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4451,37 +4463,29 @@
         </is>
       </c>
       <c r="J78" s="3" t="n"/>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>318 mm de alto: hay que partirla para la Ender 3 V2</t>
-        </is>
-      </c>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>X05</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CB-232 Soporte del imán</t>
+          <t>Tubo cuadrado de aluminio</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>30 × 30 × 2 mm, largo 440 mm</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
@@ -4492,10 +4496,14 @@
           <t>u</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Eslabón E3 (prismático J3)</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4504,47 +4512,51 @@
         </is>
       </c>
       <c r="J79" s="3" t="n"/>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>CAD: CB-401. Se desliza en el canal 31 × 31 de E2: cinta de PTFE (X06)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>X06</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>CB-301 Eslabón E2</t>
+          <t>Cinta de PTFE adhesiva</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PETG: cubo ≥ 6 perímetros 50 %, cola 3 perímetros 15 %</t>
+          <t>Ancho ≥ 20 mm</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Canal 31 × 31 de E2 (guía de J3)</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4553,51 +4565,47 @@
         </is>
       </c>
       <c r="J80" s="3" t="n"/>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>504,5 mm de largo: partir en 3 tramos (cubo del hombro + 2 tramos de cola). La cola liviana es parte del balance de J2</t>
-        </is>
-      </c>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>X07</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>CB-402 Brida de E3 (herramienta)</t>
+          <t>Precinto plástico</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>≈ 3 mm de ancho</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>2 extremos de la correa de J3 en la pinza CB-403 · 2 cámaras C270 en sus soportes</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4606,37 +4614,29 @@
         </is>
       </c>
       <c r="J81" s="3" t="n"/>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>Tapón al 100 % de relleno</t>
-        </is>
-      </c>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>X08</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>CB-303 Tapa de E2 / soporte AS5600</t>
+          <t>Tubo cuadrado de aluminio</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>20 × 20 × 1,5 mm, largo 627 mm</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
@@ -4647,10 +4647,14 @@
           <t>u</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Mástil de las cámaras</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4659,18 +4663,18 @@
         </is>
       </c>
       <c r="J82" s="3" t="n"/>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>CAD: CB-152</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4680,7 +4684,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>CB-305 Buje D8 del hombro</t>
+          <t>CB-112 Pata de la base</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4689,7 +4693,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4714,16 +4718,12 @@
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>Mejor en aluminio: transmite el torque del hombro (≈ 25 kg·cm de pico)</t>
-        </is>
-      </c>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>CB-403 Portatuerca T8</t>
+          <t>CB-121 Placa fija J1 (1M2A)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4767,16 +4767,12 @@
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %</t>
-        </is>
-      </c>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4786,7 +4782,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>CB-601 Horquilla U</t>
+          <t>CB-131 Soporte motor J1 (37D)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4825,7 +4821,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4835,7 +4831,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CB-602 Porta-servo</t>
+          <t>CB-141 Bandeja de electrónica</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4869,12 +4865,16 @@
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>210 × 100 mm</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CB-603 Caja de torsión</t>
+          <t>CB-201 Plato giratorio con dientes T5 (1M1B)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CB-604 Tapa de la caja</t>
+          <t>CB-210 Torre de cintura (2M1D mod)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4967,12 +4967,16 @@
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>318 mm de alto: hay que partirla para la Ender 3 V2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4982,7 +4986,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CB-605 Polea del servo GT2 66 dientes</t>
+          <t>CB-232 Soporte del imán</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5016,16 +5020,12 @@
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %</t>
-        </is>
-      </c>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>CB-606 Eje hueco con polea GT2 66 dientes</t>
+          <t>CB-301 Eslabón E2</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>PETG: cubo ≥ 6 perímetros 50 %, cola 3 perímetros 15 %</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
@@ -5071,14 +5071,14 @@
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 %</t>
+          <t>470 mm de largo: partir en 2 tramos (cubo del hombro hasta x ≈ −100 + cola). La cola liviana baja el torque de J2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CB-607 Separador del pivote</t>
+          <t>CB-402 Brida de E3 (herramienta)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5122,12 +5122,16 @@
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>Tapón al 100 % de relleno</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5137,7 +5141,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Anillo de retención del eje hueco</t>
+          <t>CB-303 Tapa de E2 / soporte AS5600</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5171,14 +5175,781 @@
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CB-305 Buje D8 del hombro</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Mejor en aluminio: transmite el torque del hombro (≈ 39 kg·cm de pico)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>CB-403 Tapón trasero con pinza de correa</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>CB-601 Horquilla U</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>CB-602 Porta-servo</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>CB-603 Caja de torsión</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>CB-604 Tapa de la caja</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>CB-605 Polea del servo GT2 66 dientes</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>CB-606 Eje hueco con polea GT2 66 dientes</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>CB-607 Separador del pivote</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="n"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Anillo de retención del eje hueco</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>Solo en el .scad (pieza 5), no en el STEP de la herramienta</t>
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>CB-306 Placa soporte del NEMA 17 (J3)</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %. Va a E2 con 4 insertos M3 (H26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>CB-151 Pie del mástil de las cámaras</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>CB-153 Cabezal del mástil</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %. Orejas del pivote de cabeceo M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>CB-154 Barra estéreo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="n"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %: tiene que ser rígida (si se tuerce hay que recalibrar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>CB-155 Soporte de la C270</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M92"/>
+  <autoFilter ref="A1:M107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/bom/BOM_CitriBot.xlsx
+++ b/bom/BOM_CitriBot.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$A$1:$M$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Visión estéreo, en el mástil CB-150 (a 120 mm entre lentes)</t>
+          <t>Visión estéreo, en el soporte CB-156 del mástil (71 mm entre lentes)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Precio del pedido 'Cámaras': confirmar si es por unidad o por las dos. CAD: CB-515. Quitarles la pinza de monitor</t>
+          <t>Precio del pedido 'Cámaras': confirmar si es por unidad o por las dos. CAD: CB-515. Se cuelgan con su propia pinza de monitor en la pared del soporte</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Pedido 'Ventosa 1'</t>
+          <t>Pedido 'Ventosa 1'. Su parte de arriba (Ø19, planos a 17) entra en la punta de CB-606; el racor N03 la aprieta desde adentro. CAD: CB-618 (medida, Ø40 × 22)</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Pedido 'Ventosa 2'</t>
+          <t>Pedido 'Ventosa 2'. Si su parte de arriba no es igual a la de la N01, no entra en el alojamiento de CB-606</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Macho 1/4 a manguera 6 mm (tipo PC6-02)</t>
+          <t>Recto, manguera 6 mm × rosca macho 1/4" BSP con junta tórica (0,9" de alto)</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1758,7 +1758,7 @@
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Pedido 'Unión neumática'</t>
+          <t>Pedido 'Unión neumática'. CAD: CB-619; medir hexágono (≈ 14), anillo (≈ Ø16,5 × 1,8), cuello (≈ 3) y rosca (≈ 4,5) antes de imprimir CB-606 y CB-620</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3 tapa de E2 → E2 · 4 Sabertooth → bandeja · 8 pestañas de los servos · 2 porta-servo · 4 placa CB-306 → insertos de E2 · 4 soportes C270 → barra estéreo</t>
+          <t>3 tapa de E2 → E2 · 4 Sabertooth → bandeja · 8 pestañas de los servos · 2 porta-servo · 4 placa CB-306 → insertos de E2</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Tapa de la caja de torsión</t>
+          <t>4 tapa de la caja de torsión · 4 base del soporte estéreo CB-156 → adaptador CB-154</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Soportes C270 → barra estéreo</t>
+          <t>Base del soporte estéreo → adaptador CB-154 (en los alojamientos hexagonales)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4274,26 +4274,26 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>X01</t>
+          <t>H30</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Tablero contrachapado o MDF</t>
+          <t>Tornillo autorroscante Ø3,5 × 10</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>550 × 550 × 16 mm</t>
+          <t>Cabeza plana</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Base del brazo</t>
+          <t>Tapas CB-157 → postes del soporte estéreo (agujeros de Ø3,25)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4318,44 +4318,40 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>Agujeros: Ø42 motor J1 y 4 × Ø4.5 bandeja (ver CB-111)</t>
-        </is>
-      </c>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>X02</t>
+          <t>H31</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Materia prima y consumibles</t>
+          <t>Tornillería</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Filamento PETG</t>
+          <t>Tornillo M3 × 25 Allen + tuerca M3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1,75 mm</t>
+          <t>DIN 912</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Alma del cuello de la bola de la pieza de pruebas CB-158</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4373,14 +4369,14 @@
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Estimado 3–4 kg: calcular con el slicer</t>
+          <t>Solo para las pruebas de visión sin el brazo</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>X03</t>
+          <t>X01</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4390,10 +4386,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Epoxi bicomponente</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>Tablero contrachapado o MDF</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>550 × 550 × 16 mm</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Buje D8 en E2 · brida y tapón del tubo de E3</t>
+          <t>Base del brazo</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4420,12 +4420,16 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>Agujeros: Ø42 motor J1 y 4 × Ø4.5 bandeja (ver CB-111)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>X04</t>
+          <t>X02</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4435,21 +4439,25 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Cianoacrilato</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
+          <t>Filamento PETG</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>1,75 mm</t>
+        </is>
+      </c>
       <c r="E78" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Imán en el soporte CB-232</t>
+          <t>Piezas impresas</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4465,12 +4473,16 @@
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Estimado 3–4 kg: calcular con el slicer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>X05</t>
+          <t>X03</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4480,14 +4492,10 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Tubo cuadrado de aluminio</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>30 × 30 × 2 mm, largo 440 mm</t>
-        </is>
-      </c>
+          <t>Epoxi bicomponente</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
@@ -4498,7 +4506,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Eslabón E3 (prismático J3)</t>
+          <t>Buje D8 en E2 · brida y tapón del tubo de E3</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4514,16 +4522,12 @@
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>CAD: CB-401. Se desliza en el canal 31 × 31 de E2: cinta de PTFE (X06)</t>
-        </is>
-      </c>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>X06</t>
+          <t>X04</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4533,25 +4537,21 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Cinta de PTFE adhesiva</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Ancho ≥ 20 mm</t>
-        </is>
-      </c>
+          <t>Cianoacrilato</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Canal 31 × 31 de E2 (guía de J3)</t>
+          <t>Imán en el soporte CB-232</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>X07</t>
+          <t>X05</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4582,16 +4582,16 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Precinto plástico</t>
+          <t>Tubo cuadrado de aluminio</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>≈ 3 mm de ancho</t>
+          <t>30 × 30 × 2 mm, largo 440 mm</t>
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2 extremos de la correa de J3 en la pinza CB-403 · 2 cámaras C270 en sus soportes</t>
+          <t>Eslabón E3 (prismático J3)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4616,12 +4616,16 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>CAD: CB-401. Se desliza en el canal 31 × 31 de E2: cinta de PTFE (X06)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>X08</t>
+          <t>X06</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4631,25 +4635,25 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Tubo cuadrado de aluminio</t>
+          <t>Cinta de PTFE adhesiva</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>20 × 20 × 1,5 mm, largo 627 mm</t>
+          <t>Ancho ≥ 20 mm</t>
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Mástil de las cámaras</t>
+          <t>Canal 31 × 31 de E2 (guía de J3)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4665,45 +4669,45 @@
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>CAD: CB-152</t>
-        </is>
-      </c>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>X07</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>CB-112 Pata de la base</t>
+          <t>Precinto plástico</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>≈ 3 mm de ancho</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Extremos de la correa de J3 en la pinza CB-403</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4712,33 +4716,29 @@
         </is>
       </c>
       <c r="J83" s="3" t="n"/>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>X08</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Piezas impresas</t>
+          <t>Materia prima y consumibles</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>CB-121 Placa fija J1 (1M2A)</t>
+          <t>Tubo cuadrado de aluminio</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>20 × 20 × 1,5 mm, largo 627 mm</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
@@ -4749,10 +4749,14 @@
           <t>u</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Mástil de las cámaras</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Impresión 3D</t>
+          <t>Por comprar</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4761,18 +4765,18 @@
         </is>
       </c>
       <c r="J84" s="3" t="n"/>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Impresora del grupo (Ender 3 V2)</t>
-        </is>
-      </c>
+      <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>CAD: CB-152</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>P03</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4782,7 +4786,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>CB-131 Soporte motor J1 (37D)</t>
+          <t>CB-112 Pata de la base</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4791,7 +4795,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4821,7 +4825,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4831,7 +4835,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>CB-141 Bandeja de electrónica</t>
+          <t>CB-121 Placa fija J1 (1M2A)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4865,16 +4869,12 @@
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>210 × 100 mm</t>
-        </is>
-      </c>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CB-201 Plato giratorio con dientes T5 (1M1B)</t>
+          <t>CB-131 Soporte motor J1 (37D)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>CB-210 Torre de cintura (2M1D mod)</t>
+          <t>CB-141 Bandeja de electrónica</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4969,14 +4969,14 @@
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>318 mm de alto: hay que partirla para la Ender 3 V2</t>
+          <t>210 × 100 mm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>P07</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>CB-232 Soporte del imán</t>
+          <t>CB-201 Plato giratorio con dientes T5 (1M1B)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>CB-301 Eslabón E2</t>
+          <t>CB-210 Torre de cintura (2M1D mod)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>PETG: cubo ≥ 6 perímetros 50 %, cola 3 perímetros 15 %</t>
+          <t>PETG, ≥ 4 perímetros</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
@@ -5071,14 +5071,14 @@
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>470 mm de largo: partir en 2 tramos (cubo del hombro hasta x ≈ −100 + cola). La cola liviana baja el torque de J2</t>
+          <t>318 mm de alto: hay que partirla para la Ender 3 V2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>CB-402 Brida de E3 (herramienta)</t>
+          <t>CB-232 Soporte del imán</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5122,16 +5122,12 @@
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>Tapón al 100 % de relleno</t>
-        </is>
-      </c>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5141,12 +5137,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>CB-303 Tapa de E2 / soporte AS5600</t>
+          <t>CB-301 Eslabón E2</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>PETG, ≥ 4 perímetros</t>
+          <t>PETG: cubo ≥ 6 perímetros 50 %, cola 3 perímetros 15 %</t>
         </is>
       </c>
       <c r="E92" s="2" t="n">
@@ -5175,12 +5171,16 @@
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>470 mm de largo: partir en 2 tramos (cubo del hombro hasta x ≈ −100 + cola). La cola liviana baja el torque de J2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>CB-305 Buje D8 del hombro</t>
+          <t>CB-402 Brida de E3 (herramienta)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5226,14 +5226,14 @@
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Mejor en aluminio: transmite el torque del hombro (≈ 39 kg·cm de pico)</t>
+          <t>Tapón al 100 % de relleno</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>CB-403 Tapón trasero con pinza de correa</t>
+          <t>CB-303 Tapa de E2 / soporte AS5600</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5277,16 +5277,12 @@
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %</t>
-        </is>
-      </c>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5296,7 +5292,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>CB-601 Horquilla U</t>
+          <t>CB-305 Buje D8 del hombro</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5330,12 +5326,16 @@
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Mejor en aluminio: transmite el torque del hombro (≈ 39 kg·cm de pico)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>CB-602 Porta-servo</t>
+          <t>CB-403 Tapón trasero con pinza de correa</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -5379,12 +5379,16 @@
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>P15</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5394,7 +5398,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>CB-603 Caja de torsión</t>
+          <t>CB-601 Horquilla U</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -5433,7 +5437,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5443,7 +5447,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>CB-604 Tapa de la caja</t>
+          <t>CB-602 Porta-servo</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5482,7 +5486,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5492,7 +5496,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>CB-605 Polea del servo GT2 66 dientes</t>
+          <t>CB-603 Caja de torsión</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5526,16 +5530,12 @@
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %</t>
-        </is>
-      </c>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>P18</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>CB-606 Eje hueco con polea GT2 66 dientes</t>
+          <t>CB-604 Tapa de la caja</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5579,16 +5579,12 @@
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %</t>
-        </is>
-      </c>
+      <c r="M100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>P19</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5598,7 +5594,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>CB-607 Separador del pivote</t>
+          <t>CB-605 Polea del servo GT2 66 dientes</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5632,12 +5628,16 @@
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>P20</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Anillo de retención del eje hueco</t>
+          <t>CB-606 Eje hueco con polea GT2 66 dientes</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5683,14 +5683,14 @@
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Solo en el .scad (pieza 5), no en el STEP de la herramienta</t>
+          <t>Relleno 100 %. Alojamiento doble D para la ventosa en la punta (el eje gira la ventosa) y fondo de 3 mm donde apoya el racor N03. Imprimir con la polea abajo, sin soportes. STL: cad/imprimir/CB-606_Eje_Hueco_Polea.stl</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>CB-306 Placa soporte del NEMA 17 (J3)</t>
+          <t>CB-607 Separador del pivote</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -5734,16 +5734,12 @@
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>Relleno 100 %. Va a E2 con 4 insertos M3 (H26)</t>
-        </is>
-      </c>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5753,7 +5749,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>CB-151 Pie del mástil de las cámaras</t>
+          <t>Anillo de retención del eje hueco</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5789,14 +5785,14 @@
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 %</t>
+          <t>Solo en el .scad (pieza 5), no en el STEP de la herramienta</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>P23</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5806,7 +5802,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>CB-153 Cabezal del mástil</t>
+          <t>CB-306 Placa soporte del NEMA 17 (J3)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5842,14 +5838,14 @@
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 %. Orejas del pivote de cabeceo M5</t>
+          <t>Relleno 100 %. Va a E2 con 4 insertos M3 (H26)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5859,7 +5855,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>CB-154 Barra estéreo</t>
+          <t>CB-151 Pie del mástil de las cámaras</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5895,14 +5891,14 @@
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 %: tiene que ser rígida (si se tuerce hay que recalibrar)</t>
+          <t>Relleno 100 %</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5912,7 +5908,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>CB-155 Soporte de la C270</t>
+          <t>CB-153 Cabezal del mástil</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -5921,7 +5917,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -5946,10 +5942,287 @@
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %. Orejas del pivote de cabeceo M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>CB-154 Adaptador del soporte estéreo</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="n"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Relleno 100 %. Une el pivote del cabezal con la base del soporte. STL: cad/imprimir/CB-154_Adaptador_Soporte_Estereo.stl</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>CB-156 Base del soporte estéreo (StereoVision_03)</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="n"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Remodelada del STL del usuario con los 4 agujeros para el adaptador ya hechos. STL: cad/imprimir/CB-156_Soporte_Estereo_C270_Base.stl</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>CB-157 Tapa del soporte estéreo</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>PETG, ≥ 4 perímetros</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="n"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Traba la pinza de cada C270. STL: cad/imprimir/CB-157_Soporte_Estereo_C270_Tapa.stl</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>CB-158 Adaptador con bola para la rótula del trípode (pruebas)</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>PETG, 4 perímetros, 50 %</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Probar las cámaras en el trípode antes de montar el brazo</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>No va en el robot. Bola Ø11,8 y cuello Ø4,8 en lugar del perno M6 del trípode; se cambia por CB-154 sin tocar las cámaras. Imprimir con la cara de arriba en la cama y soportes bajo la bola. STL: cad/imprimir/CB-158_Adaptador_Rotula_Bola12.stl</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Piezas impresas</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>CB-620 Llave de montaje del racor (herramienta)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>PETG, 4 perímetros, 50 %</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Apretar el racor N03 contra la ventosa desde el lado de la polea</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Impresión 3D</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Falta</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Impresora del grupo (Ender 3 V2)</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>No va en el robot. STL: cad/imprimir/CB-620_Llave_Montaje_Racor.stl</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M107"/>
+  <autoFilter ref="A1:M112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/bom/BOM_CitriBot.xlsx
+++ b/bom/BOM_CitriBot.xlsx
@@ -5683,7 +5683,7 @@
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 %. Alojamiento doble D para la ventosa en la punta (el eje gira la ventosa) y fondo de 3 mm donde apoya el racor N03. Imprimir con la polea abajo, sin soportes. STL: cad/imprimir/CB-606_Eje_Hueco_Polea.stl</t>
+          <t>Relleno 100 %. Alojamiento doble D para la ventosa en la punta (el eje gira la ventosa) y fondo de 3 mm donde apoya el racor N03. Imprimir con la polea abajo, sin soportes. STL: cad/imprimir/00_Herramienta/CB-606_Eje_Hueco_Polea.stl</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Relleno 100 %. Une el pivote del cabezal con la base del soporte. STL: cad/imprimir/CB-154_Adaptador_Soporte_Estereo.stl</t>
+          <t>Relleno 100 %. Une el pivote del cabezal con la base del soporte. STL: cad/imprimir/01_Base_J0/CB-154_Adaptador_Soporte_Estereo.stl</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Remodelada del STL del usuario con los 4 agujeros para el adaptador ya hechos. STL: cad/imprimir/CB-156_Soporte_Estereo_C270_Base.stl</t>
+          <t>Remodelada del STL del usuario con los 4 agujeros para el adaptador ya hechos. STL: cad/imprimir/01_Base_J0/CB-156_Soporte_Estereo_C270_Base.stl</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Traba la pinza de cada C270. STL: cad/imprimir/CB-157_Soporte_Estereo_C270_Tapa.stl</t>
+          <t>Traba la pinza de cada C270. STL: cad/imprimir/01_Base_J0/CB-157_Soporte_Estereo_C270_Tapa.stl</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       <c r="L111" s="2" t="inlineStr"/>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>No va en el robot. Bola Ø11,8 y cuello Ø4,8 en lugar del perno M6 del trípode; se cambia por CB-154 sin tocar las cámaras. Imprimir con la cara de arriba en la cama y soportes bajo la bola. STL: cad/imprimir/CB-158_Adaptador_Rotula_Bola12.stl</t>
+          <t>No va en el robot. Bola Ø11,8 y cuello Ø4,8 en lugar del perno M6 del trípode; se cambia por CB-154 sin tocar las cámaras. Imprimir con la cara de arriba en la cama y soportes bajo la bola. STL: cad/imprimir/12_Pruebas/CB-158_Adaptador_Rotula_Bola12.stl</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>No va en el robot. STL: cad/imprimir/CB-620_Llave_Montaje_Racor.stl</t>
+          <t>No va en el robot. STL: cad/imprimir/00_Herramienta/CB-620_Llave_Montaje_Racor.stl</t>
         </is>
       </c>
     </row>

--- a/bom/BOM_CitriBot.xlsx
+++ b/bom/BOM_CitriBot.xlsx
@@ -5481,7 +5481,11 @@
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Ranura para el cable del servo de torsión (v7.3); el cable sale por la muesca de la caja CB-603. STL: cad/imprimir/00_Herramienta/CB-602_Porta_Servo.stl</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
